--- a/#FC25_anonymized.xlsx
+++ b/#FC25_anonymized.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10357,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11667,7 +11667,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11716,7 +11716,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12901,7 +12901,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13157,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13380,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13901,7 +13901,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13944,7 +13944,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14287,7 +14287,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14375,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14504,7 +14504,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14686,7 +14686,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14736,7 +14736,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14824,7 +14824,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15103,7 +15103,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15720,7 +15720,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15764,7 +15764,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15809,7 +15809,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16099,7 +16099,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16249,7 +16249,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16393,7 +16393,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16612,7 +16612,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17107,7 +17107,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17555,7 +17555,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17641,7 +17641,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17685,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17782,7 +17782,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17824,7 +17824,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17911,7 +17911,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18008,7 +18008,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18052,7 +18052,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18222,7 +18222,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18310,7 +18310,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18438,7 +18438,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18608,7 +18608,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18746,7 +18746,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18834,7 +18834,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18920,7 +18920,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18972,7 +18972,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19300,7 +19300,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19377,7 +19377,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19415,7 +19415,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19454,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19823,7 +19823,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19905,7 +19905,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19947,7 +19947,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20031,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20073,7 +20073,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20157,7 +20157,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20283,7 +20283,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20404,7 +20404,7 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20483,7 +20483,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20522,7 +20522,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20600,7 +20600,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20727,7 +20727,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20861,7 +20861,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20904,7 +20904,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20950,7 +20950,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21083,7 +21083,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21125,7 +21125,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21163,7 +21163,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21320,7 +21320,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21399,7 +21399,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21477,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21516,7 +21516,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21559,7 +21559,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21602,7 +21602,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21688,7 +21688,7 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21774,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21817,7 +21817,7 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21860,7 +21860,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21985,7 +21985,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22025,7 +22025,7 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22065,7 +22065,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22185,7 +22185,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22265,7 +22265,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22344,7 +22344,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22387,7 +22387,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22430,7 +22430,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22514,7 +22514,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22560,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22608,7 +22608,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22656,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22695,7 +22695,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22810,7 +22810,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22851,7 +22851,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22936,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22976,7 +22976,7 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23098,7 +23098,7 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23141,7 +23141,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23186,7 +23186,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23360,7 +23360,7 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23403,7 +23403,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23445,7 +23445,7 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23488,7 +23488,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23627,7 +23627,7 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23669,7 +23669,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23711,7 +23711,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23756,7 +23756,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23842,7 +23842,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23884,7 +23884,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23926,7 +23926,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23969,7 +23969,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24012,7 +24012,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24055,7 +24055,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24099,7 +24099,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24143,7 +24143,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24188,7 +24188,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24232,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24274,7 +24274,7 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24317,7 +24317,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24361,7 +24361,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24403,7 +24403,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24445,7 +24445,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24491,7 +24491,7 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24535,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24620,7 +24620,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24664,7 +24664,7 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24707,7 +24707,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24838,7 +24838,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24923,7 +24923,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24965,7 +24965,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25009,7 +25009,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25052,7 +25052,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25096,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25138,7 +25138,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25229,7 +25229,7 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25355,7 +25355,7 @@
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25484,7 +25484,7 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25568,7 +25568,7 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25610,7 +25610,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25653,7 +25653,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25695,7 +25695,7 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25741,7 +25741,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25783,7 +25783,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25825,7 +25825,7 @@
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25867,7 +25867,7 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25909,7 +25909,7 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26035,7 +26035,7 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26077,7 +26077,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26203,7 +26203,7 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26288,7 +26288,7 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26377,7 +26377,7 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26420,7 +26420,7 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26462,7 +26462,7 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26505,7 +26505,7 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26547,7 +26547,7 @@
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26589,7 +26589,7 @@
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26633,7 +26633,7 @@
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26724,7 +26724,7 @@
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26773,7 +26773,7 @@
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26818,7 +26818,7 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26860,7 +26860,7 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26907,7 +26907,7 @@
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26998,7 +26998,7 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27091,7 @@
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27190,7 +27190,7 @@
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27307,7 +27307,7 @@
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27345,7 +27345,7 @@
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27384,7 +27384,7 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27422,7 +27422,7 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27499,7 +27499,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27587,7 +27587,7 @@
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27630,7 +27630,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27673,7 +27673,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27722,7 +27722,7 @@
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27764,7 +27764,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27806,7 +27806,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27848,7 +27848,7 @@
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27892,7 +27892,7 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27936,7 +27936,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27983,7 +27983,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28025,7 +28025,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28114,7 +28114,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28162,7 +28162,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28246,7 +28246,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28336,7 +28336,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28378,7 +28378,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28422,7 +28422,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28464,7 +28464,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28506,7 +28506,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28548,7 +28548,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28590,7 +28590,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28632,7 +28632,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28679,7 +28679,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28722,7 +28722,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28850,7 +28850,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28976,7 +28976,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29097,7 +29097,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29137,7 +29137,7 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29175,7 +29175,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
